--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kero_folder\Work\ExcelToJsonWizard\ExempleExcel\Not Include Enum\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBD9EC9-BC6F-4494-8B80-882FE04EDF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4093C9E-5123-46E0-82FB-076DAD08135C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3030" windowWidth="18735" windowHeight="14430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13170" yWindow="1755" windowWidth="15330" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,57 +25,144 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
   <si>
     <t>key</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>name</t>
-  </si>
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>scores</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>itemName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>description</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>path</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>Scores</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>85,90,75</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>95,80,70</t>
-  </si>
-  <si>
-    <t>Doe</t>
-  </si>
-  <si>
-    <t>88,89,90</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경로</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>언어별이름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템이름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용횟수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>useCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템타입</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enum&lt;ItemCarryType&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OneHanded</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TwoHanded</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cabinet</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A strange object</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battery</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electronic door lock</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bookshelf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tablet</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brick</t>
+  </si>
+  <si>
+    <t>OneHanded</t>
   </si>
 </sst>
 </file>
@@ -415,99 +502,318 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.375" customWidth="1"/>
-    <col min="4" max="4" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
+    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>10011</v>
+      </c>
+      <c r="D4" s="2">
+        <v>10012</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>2</v>
+        <v>1002</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2">
+        <v>10021</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10022</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2">
+        <v>10031</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10032</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2">
+        <v>10041</v>
+      </c>
+      <c r="D7" s="2">
+        <v>10042</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2">
+        <v>10051</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10052</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C9" s="2">
+        <v>10061</v>
+      </c>
+      <c r="D9" s="2">
+        <v>10062</v>
+      </c>
+      <c r="E9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2">
+        <v>10071</v>
+      </c>
+      <c r="D10" s="2">
+        <v>10072</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>1101</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2">
+        <v>11001</v>
+      </c>
+      <c r="D11" s="2">
+        <v>11012</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>1102</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2">
+        <v>11031</v>
+      </c>
+      <c r="D12" s="2">
+        <v>11032</v>
+      </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>1201</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="2">
+        <v>11021</v>
+      </c>
+      <c r="D13" s="2">
+        <v>11022</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard\excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4093C9E-5123-46E0-82FB-076DAD08135C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDABB46B-955F-4942-940F-A9E147548B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13170" yWindow="1755" windowWidth="15330" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5745" yWindow="2700" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>key</t>
   </si>
@@ -147,10 +147,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Bookshelf</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Tablet</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -163,6 +159,26 @@
   </si>
   <si>
     <t>OneHanded</t>
+  </si>
+  <si>
+    <t>Board</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drum can</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Box</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -502,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -724,7 +740,7 @@
         <v>1007</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C10" s="2">
         <v>10071</v>
@@ -744,62 +760,62 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>1101</v>
+        <v>1008</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2">
-        <v>11001</v>
+        <v>10081</v>
       </c>
       <c r="D11" s="2">
-        <v>11012</v>
+        <v>10082</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>1102</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
+        <v>1009</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C12" s="2">
-        <v>11031</v>
+        <v>10091</v>
       </c>
       <c r="D12" s="2">
-        <v>11032</v>
+        <v>10092</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>1201</v>
+        <v>1101</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2">
-        <v>11021</v>
+        <v>11001</v>
       </c>
       <c r="D13" s="2">
-        <v>11022</v>
+        <v>11012</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
@@ -808,6 +824,52 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>1102</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2">
+        <v>11031</v>
+      </c>
+      <c r="D14" s="2">
+        <v>11032</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>1201</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="2">
+        <v>11021</v>
+      </c>
+      <c r="D15" s="2">
+        <v>11022</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
         <v>23</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDABB46B-955F-4942-940F-A9E147548B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFD520E-1F5F-4664-BED5-BCE0EB79B71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5745" yWindow="2700" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13215" yWindow="2670" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFD520E-1F5F-4664-BED5-BCE0EB79B71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88B4D8F-AC99-4CF4-81FC-437513B45EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13215" yWindow="2670" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
   <si>
     <t>key</t>
   </si>
@@ -95,10 +95,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>type</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>아이템타입</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -178,6 +174,34 @@
   </si>
   <si>
     <t>None</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>getKeyType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>키입력타입</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enum&lt;GetKeyType&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>itemCarryType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LeftMouse</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -518,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -526,9 +550,10 @@
     <col min="4" max="4" width="11.375" customWidth="1"/>
     <col min="6" max="6" width="10.625" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,10 +573,13 @@
         <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -571,10 +599,13 @@
         <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -594,15 +625,18 @@
         <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2">
         <v>10011</v>
@@ -617,15 +651,18 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1002</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2">
         <v>10021</v>
@@ -640,15 +677,18 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1003</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2">
         <v>10031</v>
@@ -663,15 +703,18 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2">
         <v>10041</v>
@@ -686,15 +729,18 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>1005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2">
         <v>10051</v>
@@ -709,15 +755,18 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2">
         <v>10061</v>
@@ -732,15 +781,18 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="H9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>1007</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2">
         <v>10071</v>
@@ -749,21 +801,24 @@
         <v>10072</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>1008</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2">
         <v>10081</v>
@@ -772,21 +827,24 @@
         <v>10082</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>1009</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="2">
         <v>10091</v>
@@ -795,24 +853,27 @@
         <v>10092</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>1101</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2">
-        <v>11001</v>
+        <v>11011</v>
       </c>
       <c r="D13" s="2">
         <v>11012</v>
@@ -824,44 +885,50 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="H13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>1102</v>
       </c>
       <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="2">
+        <v>11021</v>
+      </c>
+      <c r="D14" s="2">
+        <v>11022</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="2">
-        <v>11031</v>
-      </c>
-      <c r="D14" s="2">
-        <v>11032</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>1201</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2">
-        <v>11021</v>
+        <v>12011</v>
       </c>
       <c r="D15" s="2">
-        <v>11022</v>
+        <v>12012</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -870,7 +937,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="H15" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88B4D8F-AC99-4CF4-81FC-437513B45EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D41DEEC-BF05-48A1-AE53-F2AF69952772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
   <si>
     <t>key</t>
   </si>
@@ -202,6 +202,13 @@
   </si>
   <si>
     <t>LeftMouse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropaneTank</t>
+  </si>
+  <si>
+    <t>s</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -209,7 +216,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,6 +235,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF27262E"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -254,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -262,6 +277,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -542,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -943,6 +959,32 @@
         <v>43</v>
       </c>
     </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>1202</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2">
+        <v>12021</v>
+      </c>
+      <c r="D16" s="2">
+        <v>12022</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D41DEEC-BF05-48A1-AE53-F2AF69952772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFA21B6-E322-4298-98B9-65141D9FD55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="660" yWindow="2580" windowWidth="15450" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="43">
   <si>
     <t>key</t>
   </si>
@@ -119,10 +119,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cabinet</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Table</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -135,14 +131,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Electronic door lock</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Tablet</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -161,54 +149,46 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Drum can</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>getKeyType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>키입력타입</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enum&lt;GetKeyType&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>itemCarryType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LeftMouse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropaneTank</t>
   </si>
   <si>
     <t>s</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Box</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>getKeyType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>키입력타입</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enum&lt;GetKeyType&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>itemCarryType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LeftMouse</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PropaneTank</t>
-  </si>
-  <si>
-    <t>s</t>
+    <t>DrumBarrel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -558,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -589,10 +569,10 @@
         <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -618,7 +598,7 @@
         <v>19</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -644,7 +624,7 @@
         <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -652,7 +632,7 @@
         <v>1001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2">
         <v>10011</v>
@@ -670,7 +650,7 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -678,7 +658,7 @@
         <v>1002</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2">
         <v>10021</v>
@@ -696,7 +676,7 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -704,7 +684,7 @@
         <v>1003</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2">
         <v>10031</v>
@@ -722,7 +702,7 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -730,7 +710,7 @@
         <v>1004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2">
         <v>10041</v>
@@ -748,7 +728,7 @@
         <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -756,16 +736,16 @@
         <v>1005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2">
-        <v>10051</v>
+        <v>10071</v>
       </c>
       <c r="D8" s="2">
-        <v>10052</v>
+        <v>10072</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -774,21 +754,21 @@
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>1006</v>
+        <v>1101</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2">
-        <v>10061</v>
+        <v>11011</v>
       </c>
       <c r="D9" s="2">
-        <v>10062</v>
+        <v>11012</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
@@ -797,24 +777,24 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>1007</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>1102</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
       </c>
       <c r="C10" s="2">
-        <v>10071</v>
+        <v>11021</v>
       </c>
       <c r="D10" s="2">
-        <v>10072</v>
+        <v>11022</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
@@ -823,165 +803,87 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>1008</v>
+        <v>1103</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2">
-        <v>10081</v>
+        <v>11031</v>
       </c>
       <c r="D11" s="2">
-        <v>10082</v>
+        <v>11032</v>
       </c>
       <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" t="s">
         <v>36</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>1009</v>
+        <v>1201</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2">
-        <v>10091</v>
+        <v>12011</v>
       </c>
       <c r="D12" s="2">
-        <v>10092</v>
+        <v>12012</v>
       </c>
       <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" t="s">
         <v>36</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>1101</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>1202</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="C13" s="2">
-        <v>11011</v>
+        <v>12021</v>
       </c>
       <c r="D13" s="2">
-        <v>11012</v>
+        <v>12022</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>1102</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="2">
-        <v>11021</v>
-      </c>
-      <c r="D14" s="2">
-        <v>11022</v>
-      </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>1201</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="2">
-        <v>12011</v>
-      </c>
-      <c r="D15" s="2">
-        <v>12012</v>
-      </c>
-      <c r="E15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>1202</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="2">
-        <v>12021</v>
-      </c>
-      <c r="D16" s="2">
-        <v>12022</v>
-      </c>
-      <c r="E16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" t="s">
         <v>20</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFA21B6-E322-4298-98B9-65141D9FD55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0B5146-429A-459A-94B8-50230B1DCFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="2580" windowWidth="15450" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
   <si>
     <t>key</t>
   </si>
@@ -149,34 +149,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>getKeyType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>키입력타입</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enum&lt;GetKeyType&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>itemCarryType</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>None</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LeftMouse</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PropaneTank</t>
   </si>
   <si>
@@ -189,6 +165,62 @@
   </si>
   <si>
     <t>Key</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상호작용텍스트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>interactText</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Door</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20001,20002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>actionText</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20009</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20003,20004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>동작텍스트(-1은 사용안함)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -249,7 +281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -258,6 +290,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -538,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -546,10 +585,11 @@
     <col min="4" max="4" width="11.375" customWidth="1"/>
     <col min="6" max="6" width="10.625" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -569,13 +609,16 @@
         <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -597,11 +640,14 @@
       <c r="G2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -623,16 +669,19 @@
       <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C4" s="2">
         <v>10011</v>
@@ -649,11 +698,14 @@
       <c r="G4" t="s">
         <v>20</v>
       </c>
-      <c r="H4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1002</v>
       </c>
@@ -675,11 +727,14 @@
       <c r="G5" t="s">
         <v>20</v>
       </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1003</v>
       </c>
@@ -701,11 +756,14 @@
       <c r="G6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1004</v>
       </c>
@@ -727,11 +785,14 @@
       <c r="G7" t="s">
         <v>20</v>
       </c>
-      <c r="H7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7">
+        <v>20005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>1005</v>
       </c>
@@ -739,10 +800,10 @@
         <v>31</v>
       </c>
       <c r="C8" s="2">
-        <v>10071</v>
+        <v>10051</v>
       </c>
       <c r="D8" s="2">
-        <v>10072</v>
+        <v>10052</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -753,100 +814,112 @@
       <c r="G8" t="s">
         <v>20</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="2">
+        <v>10061</v>
+      </c>
+      <c r="D9" s="2">
+        <v>10062</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>1101</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2">
+        <v>11011</v>
+      </c>
+      <c r="D10" s="2">
+        <v>11012</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>1102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2">
+        <v>11021</v>
+      </c>
+      <c r="D11" s="2">
+        <v>11022</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11">
+        <v>20006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>1103</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>1101</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="2">
-        <v>11011</v>
-      </c>
-      <c r="D9" s="2">
-        <v>11012</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>1102</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="2">
-        <v>11021</v>
-      </c>
-      <c r="D10" s="2">
-        <v>11022</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>1103</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="C12" s="2">
         <v>11031</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D12" s="2">
         <v>11032</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>1201</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="2">
-        <v>12011</v>
-      </c>
-      <c r="D12" s="2">
-        <v>12012</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -855,27 +928,30 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>1202</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>39</v>
+        <v>1201</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C13" s="2">
-        <v>12021</v>
+        <v>12011</v>
       </c>
       <c r="D13" s="2">
-        <v>12022</v>
+        <v>12012</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
@@ -883,8 +959,40 @@
       <c r="G13" t="s">
         <v>22</v>
       </c>
-      <c r="H13" t="s">
-        <v>20</v>
+      <c r="H13" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>1202</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2">
+        <v>12021</v>
+      </c>
+      <c r="D14" s="2">
+        <v>12022</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0B5146-429A-459A-94B8-50230B1DCFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987C86CB-56E3-4998-BF4A-FEAC87635F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -768,16 +768,16 @@
         <v>1004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2">
-        <v>10041</v>
+        <v>10051</v>
       </c>
       <c r="D7" s="2">
-        <v>10042</v>
+        <v>10052</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -786,10 +786,10 @@
         <v>20</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I7">
-        <v>20005</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -797,16 +797,16 @@
         <v>1005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2">
-        <v>10051</v>
+        <v>10061</v>
       </c>
       <c r="D8" s="2">
-        <v>10052</v>
+        <v>10062</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -815,7 +815,7 @@
         <v>20</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -823,28 +823,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>1006</v>
+        <v>1101</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2">
-        <v>10061</v>
+        <v>10071</v>
       </c>
       <c r="D9" s="2">
-        <v>10062</v>
+        <v>10072</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -852,74 +852,74 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>1101</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>1102</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
       </c>
       <c r="C10" s="2">
-        <v>11011</v>
+        <v>10081</v>
       </c>
       <c r="D10" s="2">
-        <v>11012</v>
+        <v>10082</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>44</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>20006</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>1102</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
+        <v>1103</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C11" s="2">
-        <v>11021</v>
+        <v>10091</v>
       </c>
       <c r="D11" s="2">
-        <v>11022</v>
+        <v>10092</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>44</v>
       </c>
       <c r="I11">
-        <v>20006</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2">
-        <v>11031</v>
+        <v>10041</v>
       </c>
       <c r="D12" s="2">
-        <v>11032</v>
+        <v>10042</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -934,7 +934,7 @@
         <v>44</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>20005</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -945,10 +945,10 @@
         <v>28</v>
       </c>
       <c r="C13" s="2">
-        <v>12011</v>
+        <v>10101</v>
       </c>
       <c r="D13" s="2">
-        <v>12012</v>
+        <v>10102</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
@@ -974,10 +974,10 @@
         <v>33</v>
       </c>
       <c r="C14" s="2">
-        <v>12021</v>
+        <v>10111</v>
       </c>
       <c r="D14" s="2">
-        <v>12022</v>
+        <v>10112</v>
       </c>
       <c r="E14" t="s">
         <v>34</v>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987C86CB-56E3-4998-BF4A-FEAC87635F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C4C888-6F1B-4E90-B38D-70A89CD1AF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="705" yWindow="1680" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
   <si>
     <t>key</t>
   </si>
@@ -221,6 +221,22 @@
   </si>
   <si>
     <t>동작텍스트(-1은 사용안함)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Radio</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A locked door</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20010</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -577,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -771,10 +787,10 @@
         <v>31</v>
       </c>
       <c r="C7" s="2">
-        <v>10051</v>
+        <v>10041</v>
       </c>
       <c r="D7" s="2">
-        <v>10052</v>
+        <v>10042</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>
@@ -800,10 +816,10 @@
         <v>39</v>
       </c>
       <c r="C8" s="2">
-        <v>10061</v>
+        <v>10051</v>
       </c>
       <c r="D8" s="2">
-        <v>10062</v>
+        <v>10052</v>
       </c>
       <c r="E8" t="s">
         <v>40</v>
@@ -823,28 +839,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>1101</v>
+        <v>1006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C9" s="2">
-        <v>10071</v>
+        <v>10061</v>
       </c>
       <c r="D9" s="2">
-        <v>10072</v>
+        <v>10062</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -852,45 +868,42 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>1102</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
+        <v>1007</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="C10" s="2">
-        <v>10081</v>
+        <v>10071</v>
       </c>
       <c r="D10" s="2">
-        <v>10082</v>
+        <v>10072</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10">
-        <v>20006</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2">
-        <v>10091</v>
+        <v>10081</v>
       </c>
       <c r="D11" s="2">
-        <v>10092</v>
+        <v>10082</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -904,45 +917,42 @@
       <c r="H11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I11">
-        <v>-1</v>
-      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>1104</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>1102</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
       </c>
       <c r="C12" s="2">
-        <v>10041</v>
+        <v>10091</v>
       </c>
       <c r="D12" s="2">
-        <v>10042</v>
+        <v>10092</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>44</v>
       </c>
       <c r="I12">
-        <v>20005</v>
+        <v>20006</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>1201</v>
+        <v>1103</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2">
         <v>10101</v>
@@ -957,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -968,10 +978,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>1202</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>33</v>
+        <v>1104</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C14" s="2">
         <v>10111</v>
@@ -980,18 +990,76 @@
         <v>10112</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>44</v>
       </c>
       <c r="I14">
+        <v>20005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>1201</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="2">
+        <v>10121</v>
+      </c>
+      <c r="D15" s="2">
+        <v>10122</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>1202</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="2">
+        <v>10131</v>
+      </c>
+      <c r="D16" s="2">
+        <v>10132</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16">
         <v>-1</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C4C888-6F1B-4E90-B38D-70A89CD1AF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368779F8-ABE6-4780-A557-EDFBB3729C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="705" yWindow="1680" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1050" yWindow="2280" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="57">
   <si>
     <t>key</t>
   </si>
@@ -237,6 +237,14 @@
   </si>
   <si>
     <t>20010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lock</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20001</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -593,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -891,13 +899,16 @@
       <c r="H10" s="6" t="s">
         <v>42</v>
       </c>
+      <c r="I10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>1101</v>
+        <v>1008</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C11" s="2">
         <v>10081</v>
@@ -912,18 +923,21 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="I11">
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>1102</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
+        <v>1101</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C12" s="2">
         <v>10091</v>
@@ -932,27 +946,27 @@
         <v>10092</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>44</v>
       </c>
       <c r="I12">
-        <v>20006</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>1103</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>1102</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
       </c>
       <c r="C13" s="2">
         <v>10101</v>
@@ -961,27 +975,27 @@
         <v>10102</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>44</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>20006</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2">
         <v>10111</v>
@@ -1002,15 +1016,15 @@
         <v>44</v>
       </c>
       <c r="I14">
-        <v>20005</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>1201</v>
+        <v>1104</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="2">
         <v>10121</v>
@@ -1025,21 +1039,21 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>20005</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>1202</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>33</v>
+        <v>1201</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C16" s="2">
         <v>10131</v>
@@ -1048,7 +1062,7 @@
         <v>10132</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
@@ -1057,9 +1071,38 @@
         <v>22</v>
       </c>
       <c r="H16" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>1202</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="2">
+        <v>10141</v>
+      </c>
+      <c r="D17" s="2">
+        <v>10142</v>
+      </c>
+      <c r="E17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I16">
+      <c r="I17">
         <v>-1</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368779F8-ABE6-4780-A557-EDFBB3729C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B28BF82-C673-4FE2-BB49-5F7B97FE6373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="2280" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-420" yWindow="1605" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
   <si>
     <t>key</t>
   </si>
@@ -245,6 +245,13 @@
   </si>
   <si>
     <t>20001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HackBox</t>
+  </si>
+  <si>
+    <t>20011</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -601,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -934,10 +941,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>1101</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>1009</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
       </c>
       <c r="C12" s="2">
         <v>10091</v>
@@ -952,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -963,10 +970,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>1102</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
+        <v>1101</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C13" s="2">
         <v>10101</v>
@@ -975,27 +982,27 @@
         <v>10102</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>44</v>
       </c>
       <c r="I13">
-        <v>20006</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>1103</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>1102</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
       </c>
       <c r="C14" s="2">
         <v>10111</v>
@@ -1004,27 +1011,27 @@
         <v>10112</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>44</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>20006</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2">
         <v>10121</v>
@@ -1045,15 +1052,15 @@
         <v>44</v>
       </c>
       <c r="I15">
-        <v>20005</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>1201</v>
+        <v>1104</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" s="2">
         <v>10131</v>
@@ -1068,21 +1075,21 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>20005</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>1202</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>33</v>
+        <v>1201</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C17" s="2">
         <v>10141</v>
@@ -1091,7 +1098,7 @@
         <v>10142</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2">
         <v>0</v>
@@ -1100,9 +1107,38 @@
         <v>22</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>1202</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2">
+        <v>10151</v>
+      </c>
+      <c r="D18" s="2">
+        <v>10152</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I17">
+      <c r="I18">
         <v>-1</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B28BF82-C673-4FE2-BB49-5F7B97FE6373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA92B4A-EA03-4F7B-8839-9B4CF2213885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-420" yWindow="1605" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8055" yWindow="2505" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA92B4A-EA03-4F7B-8839-9B4CF2213885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA23183-6D95-4569-A653-E2A032E4DF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8055" yWindow="2505" windowWidth="14895" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
   <si>
     <t>key</t>
   </si>
@@ -252,6 +252,10 @@
   </si>
   <si>
     <t>20011</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20012</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -991,7 +995,7 @@
         <v>21</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="I13">
         <v>-1</v>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GametubeGD\Desktop\Github\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA23183-6D95-4569-A653-E2A032E4DF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
   <si>
     <t>key</t>
   </si>
@@ -256,13 +255,17 @@
   </si>
   <si>
     <t>20012</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10052,10053,10054,10055</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -316,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -332,6 +335,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -611,13 +617,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="23.75" customWidth="1"/>
     <col min="6" max="6" width="10.625" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.125" style="6" bestFit="1" customWidth="1"/>
@@ -664,7 +670,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
@@ -722,7 +728,7 @@
         <v>10011</v>
       </c>
       <c r="D4" s="2">
-        <v>10012</v>
+        <v>-1</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
@@ -736,7 +742,7 @@
       <c r="H4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -751,7 +757,7 @@
         <v>10021</v>
       </c>
       <c r="D5" s="2">
-        <v>10022</v>
+        <v>-1</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -780,7 +786,7 @@
         <v>10031</v>
       </c>
       <c r="D6" s="2">
-        <v>10032</v>
+        <v>-1</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -809,7 +815,7 @@
         <v>10041</v>
       </c>
       <c r="D7" s="2">
-        <v>10042</v>
+        <v>-1</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>
@@ -837,8 +843,8 @@
       <c r="C8" s="2">
         <v>10051</v>
       </c>
-      <c r="D8" s="2">
-        <v>10052</v>
+      <c r="D8" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="E8" t="s">
         <v>40</v>
@@ -867,7 +873,7 @@
         <v>10061</v>
       </c>
       <c r="D9" s="2">
-        <v>10062</v>
+        <v>-1</v>
       </c>
       <c r="E9" t="s">
         <v>53</v>
@@ -896,7 +902,7 @@
         <v>10071</v>
       </c>
       <c r="D10" s="2">
-        <v>10072</v>
+        <v>-1</v>
       </c>
       <c r="E10" t="s">
         <v>53</v>
@@ -910,7 +916,7 @@
       <c r="H10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -925,7 +931,7 @@
         <v>10081</v>
       </c>
       <c r="D11" s="2">
-        <v>10082</v>
+        <v>-1</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -968,7 +974,7 @@
       <c r="H12" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>-1</v>
       </c>
     </row>
@@ -983,7 +989,7 @@
         <v>10101</v>
       </c>
       <c r="D13" s="2">
-        <v>10102</v>
+        <v>-1</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
@@ -1012,7 +1018,7 @@
         <v>10111</v>
       </c>
       <c r="D14" s="2">
-        <v>10112</v>
+        <v>-1</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1041,7 +1047,7 @@
         <v>10121</v>
       </c>
       <c r="D15" s="2">
-        <v>10122</v>
+        <v>-1</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -1070,7 +1076,7 @@
         <v>10131</v>
       </c>
       <c r="D16" s="2">
-        <v>10132</v>
+        <v>-1</v>
       </c>
       <c r="E16" t="s">
         <v>14</v>
@@ -1099,7 +1105,7 @@
         <v>10141</v>
       </c>
       <c r="D17" s="2">
-        <v>10142</v>
+        <v>-1</v>
       </c>
       <c r="E17" t="s">
         <v>14</v>
@@ -1128,7 +1134,7 @@
         <v>10151</v>
       </c>
       <c r="D18" s="2">
-        <v>10152</v>
+        <v>-1</v>
       </c>
       <c r="E18" t="s">
         <v>34</v>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="1740" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46,10 +46,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>description</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -66,10 +62,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>설명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>언어별이름</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -259,6 +251,14 @@
   </si>
   <si>
     <t>10052,10053,10054,10055</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>errorMessage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에러메시지</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -641,22 +641,22 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -667,25 +667,25 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -693,28 +693,28 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="H3" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -722,7 +722,7 @@
         <v>1001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2">
         <v>10011</v>
@@ -731,16 +731,16 @@
         <v>-1</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I4" s="2">
         <v>-1</v>
@@ -751,7 +751,7 @@
         <v>1002</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2">
         <v>10021</v>
@@ -760,16 +760,16 @@
         <v>-1</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -780,7 +780,7 @@
         <v>1003</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2">
         <v>10031</v>
@@ -789,16 +789,16 @@
         <v>-1</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -809,7 +809,7 @@
         <v>1004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2">
         <v>10041</v>
@@ -818,16 +818,16 @@
         <v>-1</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -838,25 +838,25 @@
         <v>1005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2">
         <v>10051</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -867,7 +867,7 @@
         <v>1006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" s="2">
         <v>10061</v>
@@ -876,16 +876,16 @@
         <v>-1</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -896,7 +896,7 @@
         <v>1007</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2">
         <v>10071</v>
@@ -905,16 +905,16 @@
         <v>-1</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I10" s="2">
         <v>-1</v>
@@ -925,7 +925,7 @@
         <v>1008</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C11" s="2">
         <v>10081</v>
@@ -934,16 +934,16 @@
         <v>-1</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -954,7 +954,7 @@
         <v>1009</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2">
         <v>10091</v>
@@ -963,16 +963,16 @@
         <v>10092</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I12" s="2">
         <v>-1</v>
@@ -983,7 +983,7 @@
         <v>1101</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2">
         <v>10101</v>
@@ -992,16 +992,16 @@
         <v>-1</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1012,7 +1012,7 @@
         <v>1102</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2">
         <v>10111</v>
@@ -1021,16 +1021,16 @@
         <v>-1</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I14">
         <v>20006</v>
@@ -1041,7 +1041,7 @@
         <v>1103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2">
         <v>10121</v>
@@ -1050,16 +1050,16 @@
         <v>-1</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1070,7 +1070,7 @@
         <v>1104</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C16" s="2">
         <v>10131</v>
@@ -1079,16 +1079,16 @@
         <v>-1</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I16">
         <v>20005</v>
@@ -1099,7 +1099,7 @@
         <v>1201</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C17" s="2">
         <v>10141</v>
@@ -1108,16 +1108,16 @@
         <v>-1</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F17" s="2">
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -1128,7 +1128,7 @@
         <v>1202</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2">
         <v>10151</v>
@@ -1137,16 +1137,16 @@
         <v>-1</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I18">
         <v>-1</v>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="2670" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="3600" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -931,7 +931,7 @@
         <v>10081</v>
       </c>
       <c r="D11" s="2">
-        <v>-1</v>
+        <v>10082</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="4530" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
   <si>
     <t>key</t>
   </si>
@@ -259,6 +259,10 @@
   </si>
   <si>
     <t>에러메시지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10102,10103</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -988,8 +992,8 @@
       <c r="C13" s="2">
         <v>10101</v>
       </c>
-      <c r="D13" s="2">
-        <v>-1</v>
+      <c r="D13" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="5460" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="6390" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="64">
   <si>
     <t>key</t>
   </si>
@@ -147,27 +147,75 @@
     <t>PropaneTank</t>
   </si>
   <si>
+    <t>DrumBarrel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상호작용텍스트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>interactText</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Door</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>s</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DrumBarrel</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Key</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>상호작용텍스트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>interactText</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Door</t>
+    <t>List&lt;int&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20001,20002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>actionText</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20009</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20003,20004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>동작텍스트(-1은 사용안함)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Radio</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A locked door</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -175,58 +223,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>List&lt;int&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20001,20002</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20007</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20008</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>actionText</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20009</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20003,20004</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>동작텍스트(-1은 사용안함)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Radio</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A locked door</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>s</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>20010</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -262,7 +258,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>10102,10103</t>
+    <t>Save</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20013</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11002,11003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10102</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -622,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -645,7 +653,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
@@ -657,10 +665,10 @@
         <v>30</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -674,7 +682,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>8</v>
@@ -686,10 +694,10 @@
         <v>17</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -703,7 +711,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>9</v>
@@ -715,10 +723,10 @@
         <v>16</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -726,7 +734,7 @@
         <v>1001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2">
         <v>10011</v>
@@ -744,7 +752,7 @@
         <v>18</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I4" s="2">
         <v>-1</v>
@@ -773,7 +781,7 @@
         <v>18</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -802,7 +810,7 @@
         <v>18</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -831,7 +839,7 @@
         <v>18</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -842,16 +850,16 @@
         <v>1005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2">
         <v>10051</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -860,7 +868,7 @@
         <v>18</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -871,7 +879,7 @@
         <v>1006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2">
         <v>10061</v>
@@ -880,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -889,7 +897,7 @@
         <v>18</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -900,7 +908,7 @@
         <v>1007</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2">
         <v>10071</v>
@@ -909,7 +917,7 @@
         <v>-1</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -918,7 +926,7 @@
         <v>18</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I10" s="2">
         <v>-1</v>
@@ -929,7 +937,7 @@
         <v>1008</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="2">
         <v>10081</v>
@@ -947,7 +955,7 @@
         <v>18</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -958,7 +966,7 @@
         <v>1009</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C12" s="2">
         <v>10091</v>
@@ -976,7 +984,7 @@
         <v>18</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I12" s="2">
         <v>-1</v>
@@ -984,16 +992,16 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>1101</v>
+        <v>1010</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C13" s="2">
         <v>10101</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -1002,10 +1010,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1013,42 +1021,42 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>1102</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
+        <v>1101</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C14" s="2">
-        <v>10111</v>
-      </c>
-      <c r="D14" s="2">
-        <v>-1</v>
+        <v>11001</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="I14">
-        <v>20006</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>1103</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>1102</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
       </c>
       <c r="C15" s="2">
-        <v>10121</v>
+        <v>11011</v>
       </c>
       <c r="D15" s="2">
         <v>-1</v>
@@ -1060,24 +1068,24 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>20006</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2">
-        <v>10131</v>
+        <v>11021</v>
       </c>
       <c r="D16" s="2">
         <v>-1</v>
@@ -1092,21 +1100,21 @@
         <v>19</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I16">
-        <v>20005</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>1201</v>
+        <v>1104</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" s="2">
-        <v>10141</v>
+        <v>11031</v>
       </c>
       <c r="D17" s="2">
         <v>-1</v>
@@ -1118,30 +1126,30 @@
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>20005</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>1202</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>31</v>
+        <v>1201</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C18" s="2">
-        <v>10151</v>
+        <v>11041</v>
       </c>
       <c r="D18" s="2">
         <v>-1</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F18" s="2">
         <v>0</v>
@@ -1150,9 +1158,38 @@
         <v>20</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>1202</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="2">
+        <v>11051</v>
+      </c>
+      <c r="D19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I19">
         <v>-1</v>
       </c>
     </row>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="6390" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="7320" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -270,7 +270,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>10102</t>
+    <t>10102,10103</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/ItemTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="8250" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="64">
   <si>
     <t>key</t>
   </si>
@@ -630,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -1137,13 +1137,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>1201</v>
+        <v>1105</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2">
-        <v>11041</v>
+        <v>11021</v>
       </c>
       <c r="D18" s="2">
         <v>-1</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -1166,13 +1166,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>1202</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>31</v>
+        <v>1201</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C19" s="2">
-        <v>11051</v>
+        <v>11041</v>
       </c>
       <c r="D19" s="2">
         <v>-1</v>
@@ -1187,9 +1187,38 @@
         <v>20</v>
       </c>
       <c r="H19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>1202</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="2">
+        <v>11051</v>
+      </c>
+      <c r="D20" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="I19">
+      <c r="I20">
         <v>-1</v>
       </c>
     </row>
